--- a/Result/profitability/4532.xlsx
+++ b/Result/profitability/4532.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.435</v>
+        <v>0.46375</v>
       </c>
       <c r="N2" t="n">
-        <v>15.51375</v>
+        <v>15.4275</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="N3" t="n">
-        <v>14.7775</v>
+        <v>14.49</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.32375</v>
+        <v>0.29875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.9325</v>
+        <v>12.55625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.165</v>
+        <v>0.17375</v>
       </c>
       <c r="N5" t="n">
-        <v>10.175</v>
+        <v>9.799999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09125000000000001</v>
+        <v>0.11875</v>
       </c>
       <c r="N6" t="n">
-        <v>8.365</v>
+        <v>8.245000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0125</v>
+        <v>0.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7.0075</v>
+        <v>6.6125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0925</v>
+        <v>-0.08624999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>5.685</v>
+        <v>5.675000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1225</v>
       </c>
       <c r="N10" t="n">
-        <v>4.69625</v>
+        <v>4.696250000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4532</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6325</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5439</v>
+      </c>
+      <c r="E75" t="n">
+        <v>886</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="G75" t="n">
+        <v>351</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>379</v>
+      </c>
+      <c r="K75" t="n">
+        <v>258</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005677785663591228</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1521739130434783</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.000000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1763668430335098</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
